--- a/CoursePatterns/Output/subject_taken_together_per_semester.xlsx
+++ b/CoursePatterns/Output/subject_taken_together_per_semester.xlsx
@@ -1374,12 +1374,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COSE214</t>
+          <t>COSE211, COSE215</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COSE213</t>
+          <t>COSE221</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1389,7 +1389,7 @@
         <v>0.7059</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3797</v>
+        <v>1.6863</v>
       </c>
     </row>
     <row r="32">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COSE215</t>
+          <t>COSE213</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1410,18 +1410,18 @@
         <v>0.7059</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2647</v>
+        <v>1.3797</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COSE211, COSE215</t>
+          <t>COSE214</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COSE221</t>
+          <t>COSE215</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1431,7 +1431,7 @@
         <v>0.7059</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6863</v>
+        <v>1.2647</v>
       </c>
     </row>
     <row r="34">
@@ -1479,75 +1479,75 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>COSE211, COSE213, COSE215</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>COSE221</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>COSE211, COSE215</t>
-        </is>
-      </c>
       <c r="C36" t="n">
-        <v>0.2791</v>
+        <v>0.2326</v>
       </c>
       <c r="D36" t="n">
         <v>0.6667</v>
       </c>
       <c r="E36" t="n">
-        <v>1.6863</v>
+        <v>1.5926</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COSE214, COSE215</t>
+          <t>COSE221</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COSE211</t>
+          <t>COSE213, COSE215</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.186</v>
+        <v>0.2791</v>
       </c>
       <c r="D37" t="n">
         <v>0.6667</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3651</v>
+        <v>1.6863</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COSE221</t>
+          <t>COSE213, COSE214</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COSE213, COSE215</t>
+          <t>COSE211</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.2791</v>
+        <v>0.186</v>
       </c>
       <c r="D38" t="n">
         <v>0.6667</v>
       </c>
       <c r="E38" t="n">
-        <v>1.6863</v>
+        <v>1.3651</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COSE213, COSE214</t>
+          <t>COSE214, COSE215</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COSE215</t>
+          <t>COSE211</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1557,7 +1557,7 @@
         <v>0.6667</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1944</v>
+        <v>1.3651</v>
       </c>
     </row>
     <row r="40">
@@ -1584,49 +1584,49 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>COSE213, COSE214</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>COSE215</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>COSE221</t>
-        </is>
-      </c>
       <c r="C41" t="n">
-        <v>0.3721</v>
+        <v>0.186</v>
       </c>
       <c r="D41" t="n">
         <v>0.6667</v>
       </c>
       <c r="E41" t="n">
-        <v>1.5926</v>
+        <v>1.1944</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COSE213, COSE214</t>
+          <t>COSE221</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COSE211</t>
+          <t>COSE211, COSE215</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.186</v>
+        <v>0.2791</v>
       </c>
       <c r="D42" t="n">
         <v>0.6667</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3651</v>
+        <v>1.6863</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COSE211, COSE213, COSE215</t>
+          <t>COSE215</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.2326</v>
+        <v>0.3721</v>
       </c>
       <c r="D43" t="n">
         <v>0.6667</v>
@@ -1647,7 +1647,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COSE215</t>
+          <t>COSE215, COSE221</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.3488</v>
+        <v>0.2326</v>
       </c>
       <c r="D44" t="n">
         <v>0.625</v>
@@ -1668,7 +1668,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COSE215, COSE221</t>
+          <t>COSE215</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2326</v>
+        <v>0.3488</v>
       </c>
       <c r="D45" t="n">
         <v>0.625</v>
